--- a/research/traditional_assets/database/data/malta/malta_real_estate_development.xlsx
+++ b/research/traditional_assets/database/data/malta/malta_real_estate_development.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0824</v>
+        <v>-0.386</v>
       </c>
       <c r="G2">
-        <v>0.4966740576496675</v>
+        <v>-0.07753424657534246</v>
       </c>
       <c r="H2">
-        <v>0.4966740576496675</v>
+        <v>-0.07753424657534246</v>
       </c>
       <c r="I2">
-        <v>-0.04060606000717374</v>
+        <v>-0.2114906742672746</v>
       </c>
       <c r="J2">
-        <v>-0.04060606000717374</v>
+        <v>-0.2114906742672746</v>
       </c>
       <c r="K2">
-        <v>-0.975</v>
+        <v>-3.11</v>
       </c>
       <c r="L2">
-        <v>-0.2161862527716186</v>
+        <v>-0.8520547945205479</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>6.07</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="V2">
-        <v>0.09019316493313523</v>
+        <v>0.1138964577656676</v>
       </c>
       <c r="W2">
-        <v>-0.007998359310910582</v>
+        <v>-0.02922932330827067</v>
       </c>
       <c r="X2">
-        <v>0.1032376877849238</v>
+        <v>0.0835551679934248</v>
       </c>
       <c r="Y2">
-        <v>-0.1112360470958344</v>
+        <v>-0.1127844913016955</v>
       </c>
       <c r="Z2">
-        <v>0.02323177516336287</v>
+        <v>0.02082920734253997</v>
       </c>
       <c r="AA2">
-        <v>-0.0009433508563566812</v>
+        <v>-0.004405183105326647</v>
       </c>
       <c r="AB2">
-        <v>0.07253037509756935</v>
+        <v>0.06107640031476584</v>
       </c>
       <c r="AC2">
-        <v>-0.07347372595392603</v>
+        <v>-0.06548158342009248</v>
       </c>
       <c r="AD2">
-        <v>74.90000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="AE2">
-        <v>0.0306666531617678</v>
+        <v>0.004704805377761328</v>
       </c>
       <c r="AF2">
-        <v>74.93066665316178</v>
+        <v>81.30470480537775</v>
       </c>
       <c r="AG2">
-        <v>68.86066665316179</v>
+        <v>72.94470480537775</v>
       </c>
       <c r="AH2">
-        <v>0.5268249697224917</v>
+        <v>0.5255477194934765</v>
       </c>
       <c r="AI2">
-        <v>0.4132266650543153</v>
+        <v>0.4263382221657964</v>
       </c>
       <c r="AJ2">
-        <v>0.5057309746328476</v>
+        <v>0.4984444425398659</v>
       </c>
       <c r="AK2">
-        <v>0.3929042834775701</v>
+        <v>0.4000374175012865</v>
       </c>
       <c r="AL2">
-        <v>2.5</v>
+        <v>2.74</v>
       </c>
       <c r="AM2">
-        <v>2.414</v>
+        <v>2.728</v>
       </c>
       <c r="AN2">
-        <v>-985.5263157894738</v>
+        <v>-120.0886262924668</v>
       </c>
       <c r="AO2">
-        <v>-0.08120000000000001</v>
+        <v>-0.2832116788321168</v>
       </c>
       <c r="AP2">
-        <v>-906.0614033310761</v>
+        <v>-107.7469790330543</v>
       </c>
       <c r="AQ2">
-        <v>-0.08409279204639603</v>
+        <v>-0.2844574780058651</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0824</v>
+        <v>-0.386</v>
       </c>
       <c r="G3">
-        <v>0.4966740576496675</v>
+        <v>-0.07753424657534246</v>
       </c>
       <c r="H3">
-        <v>0.4966740576496675</v>
+        <v>-0.07753424657534246</v>
       </c>
       <c r="I3">
-        <v>-0.04060606000717374</v>
+        <v>-0.2114906742672746</v>
       </c>
       <c r="J3">
-        <v>-0.04060606000717374</v>
+        <v>-0.2114906742672746</v>
       </c>
       <c r="K3">
-        <v>-0.975</v>
+        <v>-3.11</v>
       </c>
       <c r="L3">
-        <v>-0.2161862527716186</v>
+        <v>-0.8520547945205479</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>6.07</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="V3">
-        <v>0.09019316493313523</v>
+        <v>0.1138964577656676</v>
       </c>
       <c r="W3">
-        <v>-0.007998359310910582</v>
+        <v>-0.02922932330827067</v>
       </c>
       <c r="X3">
-        <v>0.1032376877849238</v>
+        <v>0.0835551679934248</v>
       </c>
       <c r="Y3">
-        <v>-0.1112360470958344</v>
+        <v>-0.1127844913016955</v>
       </c>
       <c r="Z3">
-        <v>0.02323177516336287</v>
+        <v>0.02082920734253997</v>
       </c>
       <c r="AA3">
-        <v>-0.0009433508563566812</v>
+        <v>-0.004405183105326647</v>
       </c>
       <c r="AB3">
-        <v>0.07253037509756935</v>
+        <v>0.06107640031476584</v>
       </c>
       <c r="AC3">
-        <v>-0.07347372595392603</v>
+        <v>-0.06548158342009248</v>
       </c>
       <c r="AD3">
-        <v>74.90000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="AE3">
-        <v>0.0306666531617678</v>
+        <v>0.004704805377761328</v>
       </c>
       <c r="AF3">
-        <v>74.93066665316178</v>
+        <v>81.30470480537775</v>
       </c>
       <c r="AG3">
-        <v>68.86066665316179</v>
+        <v>72.94470480537775</v>
       </c>
       <c r="AH3">
-        <v>0.5268249697224917</v>
+        <v>0.5255477194934765</v>
       </c>
       <c r="AI3">
-        <v>0.4132266650543153</v>
+        <v>0.4263382221657964</v>
       </c>
       <c r="AJ3">
-        <v>0.5057309746328476</v>
+        <v>0.4984444425398659</v>
       </c>
       <c r="AK3">
-        <v>0.3929042834775701</v>
+        <v>0.4000374175012865</v>
       </c>
       <c r="AL3">
-        <v>2.5</v>
+        <v>2.74</v>
       </c>
       <c r="AM3">
-        <v>2.414</v>
+        <v>2.728</v>
       </c>
       <c r="AN3">
-        <v>-985.5263157894738</v>
+        <v>-120.0886262924668</v>
       </c>
       <c r="AO3">
-        <v>-0.08120000000000001</v>
+        <v>-0.2832116788321168</v>
       </c>
       <c r="AP3">
-        <v>-906.0614033310761</v>
+        <v>-107.7469790330543</v>
       </c>
       <c r="AQ3">
-        <v>-0.08409279204639603</v>
+        <v>-0.2844574780058651</v>
       </c>
     </row>
   </sheetData>
